--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.6527777777777778</v>
+        <v>0.8160919540229885</v>
       </c>
       <c r="B2">
-        <v>0.0625</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.6126760563380281</v>
+        <v>0.6690140845070423</v>
       </c>
       <c r="D2">
-        <v>0.5288461538461539</v>
+        <v>0.3983050847457627</v>
       </c>
       <c r="E2">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>38</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_aae.xlsx
@@ -420,22 +420,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.8160919540229885</v>
+        <v>0.8117647058823529</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.6690140845070423</v>
+        <v>0.6549295774647887</v>
       </c>
       <c r="D2">
-        <v>0.3983050847457627</v>
+        <v>0.4152542372881356</v>
       </c>
       <c r="E2">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G2">
         <v>24</v>
